--- a/app/reports/MPB_research.xlsx
+++ b/app/reports/MPB_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>36.18</v>
+        <v>36.4</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.777</v>
+        <v>0.766</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>25335215.47816473</v>
+        <v>25335217.58241758</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>36.18</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="38">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>916628096</v>
+        <v>922201920</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.56</v>
+        <v>12.47</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>957640192</v>
+        <v>966342144</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>10.85728</v>
+        <v>10.955939</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>5.575</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>843000960</v>
+        <v>849846272</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>13.570247</v>
+        <v>13.568306</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>1.84</v>
+        <v>1.899</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>905048320</v>
+        <v>907695744</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>15.14557</v>
+        <v>15.189873</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>1.66</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>855781184</v>
+        <v>863845312</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>13.088333</v>
+        <v>13.211666</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>5.275</v>
+        <v>5.331</v>
       </c>
     </row>
     <row r="10">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>762865216</v>
+        <v>770305344</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.110236</v>
+        <v>12.228347</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>3.149</v>
+        <v>3.188</v>
       </c>
     </row>
     <row r="11">
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>1096521472</v>
+        <v>1106501632</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>11.310102</v>
+        <v>11.413043</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>2.817</v>
+        <v>2.882</v>
       </c>
     </row>
     <row r="13">
@@ -1690,14 +1690,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>1003889280</v>
+        <v>1013962624</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>12.111111</v>
+        <v>12.232638</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>6.049</v>
+        <v>6.135</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MPB_research.xlsx
+++ b/app/reports/MPB_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
         <v>849846272</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>13.568306</v>
+        <v>13.794445</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">

--- a/app/reports/MPB_research.xlsx
+++ b/app/reports/MPB_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>64.29000000000001</v>
+        <v>63.54</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>36.4</v>
+        <v>36.49</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.766</v>
+        <v>0.741</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05341000080108643</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>25335217.58241758</v>
+        <v>25335216.44286106</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>36.4</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>922201920</v>
+        <v>924482048</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.47</v>
+        <v>12.76</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>966342144</v>
+        <v>962624832</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>10.955939</v>
+        <v>10.913794</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>849846272</v>
+        <v>845482368</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>13.794445</v>
+        <v>13.723611</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>907695744</v>
+        <v>905048320</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>15.189873</v>
+        <v>15.097792</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>863845312</v>
+        <v>863082496</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>13.211666</v>
+        <v>13.2</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>770305344</v>
+        <v>769313344</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.228347</v>
+        <v>12.212598</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>1106501632</v>
+        <v>1093857280</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>11.413043</v>
+        <v>11.311551</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>1013962624</v>
+        <v>1010221056</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>12.232638</v>
+        <v>12.187499</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">

--- a/app/reports/MPB_research.xlsx
+++ b/app/reports/MPB_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>63.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>36.49</v>
+        <v>36.39</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.741</v>
+        <v>0.767</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05341000080108643</v>
+        <v>0.05276999950408936</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>25335216.44286106</v>
+        <v>25335215.16900247</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>36.49</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>924482048</v>
+        <v>921948480</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.76</v>
+        <v>12.72</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>962624832</v>
+        <v>957217792</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>10.913794</v>
+        <v>10.852491</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>5.625</v>
+        <v>5.611</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>845482368</v>
+        <v>846765888</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>13.723611</v>
+        <v>13.744445</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>1.899</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>905048320</v>
+        <v>906939328</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>15.097792</v>
+        <v>15.129337</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>1.704</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>863082496</v>
+        <v>866896704</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>13.2</v>
+        <v>13.258334</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>5.331</v>
+        <v>5.341</v>
       </c>
     </row>
     <row r="10">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>769313344</v>
+        <v>781217600</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.212598</v>
+        <v>12.401575</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>3.188</v>
+        <v>3.184</v>
       </c>
     </row>
     <row r="11">
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>1093857280</v>
+        <v>1100302848</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>11.311551</v>
+        <v>11.378205</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>2.882</v>
+        <v>2.854</v>
       </c>
     </row>
     <row r="13">
@@ -1690,14 +1690,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>1010221056</v>
+        <v>1007342976</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>12.187499</v>
+        <v>12.152778</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>6.135</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MPB_research.xlsx
+++ b/app/reports/MPB_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>64.29000000000001</v>
+        <v>64.31</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>36.39</v>
+        <v>35.98</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.767</v>
+        <v>0.787</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05275000095367432</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>25335215.16900247</v>
+        <v>25335216.45358533</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>36.39</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>921948480</v>
+        <v>911561088</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.72</v>
+        <v>12.58</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
@@ -1533,171 +1533,177 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>AMTB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camden National Corporation</t>
+          <t>Amerant Bancorp Inc.</t>
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>957217792</v>
+        <v>1129843584</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>10.852491</v>
+        <v>20.741007</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>5.611</v>
+        <v>4.489</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CCBG</t>
+          <t>CPF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital City Bank Group</t>
+          <t xml:space="preserve">Central Pacific Financial Corp </t>
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>846765888</v>
+        <v>923817856</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>13.744445</v>
+        <v>11.500001</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>1.875</v>
+        <v>2.242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Community Bankshares, Inc</t>
+          <t>Citizens Financial Services, In</t>
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>906939328</v>
+        <v>383706176</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>15.129337</v>
+        <v>9.330409</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>1.692</v>
+        <v>6.375</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSBC</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Great Southern Bancorp, Inc.</t>
+          <t>Citizens &amp; Northern Corp</t>
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>866896704</v>
+        <v>456083712</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>13.258334</v>
+        <v>17.29932</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>5.341</v>
+        <v>4.271</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HTB</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HomeTrust Bancshares, Inc.</t>
+          <t>Fidelity D &amp; D Bancorp, Inc.</t>
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>781217600</v>
+        <v>323940480</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.401575</v>
+        <v>10.602661</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>3.184</v>
+        <v>2.589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HTBK</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HTBK</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="34" t="n"/>
+          <t>Franklin Financial Services Cor</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>284598560</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>11.541971</v>
+      </c>
       <c r="E11" s="34" t="n"/>
-      <c r="F11" s="34" t="n"/>
+      <c r="F11" s="34" t="n">
+        <v>5.191</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>GSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Metropolitan Bank Holding Corp.</t>
+          <t>Great Southern Bancorp, Inc.</t>
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>1100302848</v>
+        <v>855617728</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>11.378205</v>
+        <v>13.085834</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>2.854</v>
+        <v>5.328</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MCBS</t>
+          <t>NBN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MetroCity Bankshares, Inc.</t>
+          <t>Northeast Bank</t>
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>1007342976</v>
+        <v>1078488704</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>12.152778</v>
+        <v>9.894819</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>6.11</v>
+        <v>6.336</v>
       </c>
     </row>
     <row r="15">
@@ -1745,11 +1751,11 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">
-        <v>0.6</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="18">

--- a/app/reports/MPB_research.xlsx
+++ b/app/reports/MPB_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>64.31</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>35.98</v>
+        <v>36.3</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.787</v>
+        <v>0.783</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05275000095367432</v>
+        <v>0.05238999843597412</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>25335216.45358533</v>
+        <v>25335216.30853995</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>35.98</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="38">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>911561088</v>
+        <v>919668352</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.58</v>
+        <v>12.69</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>1129843584</v>
+        <v>1143168128</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>20.741007</v>
+        <v>20.985611</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>4.489</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>923817856</v>
+        <v>933344384</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>11.500001</v>
+        <v>11.61859</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>2.242</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>383706176</v>
+        <v>383201152</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>9.330409</v>
+        <v>9.318129000000001</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>6.375</v>
+        <v>6.345</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>456083712</v>
+        <v>455724992</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>17.29932</v>
+        <v>17.285713</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>4.271</v>
+        <v>4.239</v>
       </c>
     </row>
     <row r="10">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>323940480</v>
+        <v>328529216</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>10.602661</v>
+        <v>10.7528515</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>2.589</v>
+        <v>2.622</v>
       </c>
     </row>
     <row r="11">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>284598560</v>
+        <v>287343296</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>11.541971</v>
+        <v>11.653285</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>5.191</v>
+        <v>5.187</v>
       </c>
     </row>
     <row r="12">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>855617728</v>
+        <v>860194688</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>13.085834</v>
+        <v>13.155833</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>5.328</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="13">
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>1078488704</v>
+        <v>1077205376</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>9.894819</v>
+        <v>9.883046</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>6.336</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="15">
